--- a/documents/db.xlsx
+++ b/documents/db.xlsx
@@ -5,16 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hassan/repos/trmnl-plugin/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hassan/repos/trmnl-plugin/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A948ACA-2BFD-6843-8570-8E10FBB35A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96942731-73D7-D94D-A89F-17E9A3786AD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5180" yWindow="1880" windowWidth="28040" windowHeight="17180" xr2:uid="{A575319D-8482-3342-9B2A-BCAC55F79057}"/>
+    <workbookView xWindow="1920" yWindow="600" windowWidth="34560" windowHeight="21000" activeTab="2" xr2:uid="{A575319D-8482-3342-9B2A-BCAC55F79057}"/>
   </bookViews>
   <sheets>
     <sheet name="Values" sheetId="1" r:id="rId1"/>
-    <sheet name="Mindest" sheetId="2" r:id="rId2"/>
+    <sheet name="Mindests" sheetId="2" r:id="rId2"/>
     <sheet name="Rituals" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
@@ -41,19 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>arabic</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>Mercy &amp; Compation</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="153">
   <si>
     <t>To be merciful and compassionate towards yourself and others</t>
   </si>
@@ -64,21 +52,9 @@
     <t>To take responsibility for your actions and not blame others</t>
   </si>
   <si>
-    <t>Truthfulness</t>
-  </si>
-  <si>
-    <t>To be truthful with yourself, and in your intentions, words, and actions. To avoid lying to yourself or others</t>
-  </si>
-  <si>
-    <t>Mindset</t>
-  </si>
-  <si>
     <t>Gratefulness</t>
   </si>
   <si>
-    <t>to be mindfully grateful to Allah for the seen and hidden blessings, favors and opportunities, and greatful to people around you.</t>
-  </si>
-  <si>
     <t>Humbleness to Allah</t>
   </si>
   <si>
@@ -88,31 +64,442 @@
     <t>Hereafter-focused</t>
   </si>
   <si>
-    <t>To always work for the eternal afterlife and consider the Akhirah-outcome of actions.</t>
-  </si>
-  <si>
-    <t>Ritual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">arabic </t>
-  </si>
-  <si>
-    <t>Tawnah &amp; Constant Return to Allah</t>
-  </si>
-  <si>
     <t>To come back humbly to Allah and repent regularly for our sins</t>
   </si>
   <si>
     <t>Reconciliation</t>
   </si>
   <si>
-    <t>To work on making things right between people who are in disagreement</t>
-  </si>
-  <si>
-    <t>Makin Dua</t>
-  </si>
-  <si>
     <t>To make dua and ask Allah for help in your daily affairs (big or small)</t>
+  </si>
+  <si>
+    <t>Mercy &amp; Compassion</t>
+  </si>
+  <si>
+    <t>الرحمة</t>
+  </si>
+  <si>
+    <t>Peace</t>
+  </si>
+  <si>
+    <t>To have inner peace and be a source of peace – not fear/stess – for others</t>
+  </si>
+  <si>
+    <t>االسلام</t>
+  </si>
+  <si>
+    <t>Truthfullness</t>
+  </si>
+  <si>
+    <t>To be truthful with yourself, and in your intentions, words, and actions. To avoid lying to yourself and others</t>
+  </si>
+  <si>
+    <t>االصدق / السعي للحق</t>
+  </si>
+  <si>
+    <t>Family</t>
+  </si>
+  <si>
+    <t>To prioritize and give due time, attention, and support to family: parents, spouce, children, and next of kin</t>
+  </si>
+  <si>
+    <t>االاهل / الارحام</t>
+  </si>
+  <si>
+    <t>Modesty &amp; Concealment</t>
+  </si>
+  <si>
+    <t>To embody modesty and cover the faults and flaws of others</t>
+  </si>
+  <si>
+    <t>االحياء و الستر</t>
+  </si>
+  <si>
+    <t>Beauty</t>
+  </si>
+  <si>
+    <t>To beautify your thoughts, hearts, words, actions, and relationships</t>
+  </si>
+  <si>
+    <t>االجمال</t>
+  </si>
+  <si>
+    <t>Justice</t>
+  </si>
+  <si>
+    <t>To speak and act justly even if against yourself.</t>
+  </si>
+  <si>
+    <t>االقسط و العدل</t>
+  </si>
+  <si>
+    <t>Generosity</t>
+  </si>
+  <si>
+    <t>To give others from your time, wealth, knowledge, and experience (and expect nothing in return)</t>
+  </si>
+  <si>
+    <t>االكرم</t>
+  </si>
+  <si>
+    <t>Excellence</t>
+  </si>
+  <si>
+    <t>To seek excellence in thoughts, words, and actions by recognizing that Allah sees you even if you don't see him</t>
+  </si>
+  <si>
+    <t>الاحسان</t>
+  </si>
+  <si>
+    <t>Strength</t>
+  </si>
+  <si>
+    <t>To seek spiritual, physical, intellectual, and all forms of strength and use that for the sake of Allah, not to harm/opress others</t>
+  </si>
+  <si>
+    <t>القوة</t>
+  </si>
+  <si>
+    <t>Uprightness</t>
+  </si>
+  <si>
+    <t>To do what's right morally, ethically, and honestly in all situations</t>
+  </si>
+  <si>
+    <t>الرشد</t>
+  </si>
+  <si>
+    <t>Trustworthiness</t>
+  </si>
+  <si>
+    <t>To consistently fulfill your promises, contracts, and trust on time and to the best of your ability</t>
+  </si>
+  <si>
+    <t>الامانة</t>
+  </si>
+  <si>
+    <t>Easiness</t>
+  </si>
+  <si>
+    <t>To be easy, down-to-earth and apporchable</t>
+  </si>
+  <si>
+    <t>السهولة و اللين</t>
+  </si>
+  <si>
+    <t>Moderation</t>
+  </si>
+  <si>
+    <t>To avoid excessiveness in all matters and seek the middle path</t>
+  </si>
+  <si>
+    <t>الاعتدال / الاقتصاد</t>
+  </si>
+  <si>
+    <t>Gentlness</t>
+  </si>
+  <si>
+    <t>To be gentle in words and actions</t>
+  </si>
+  <si>
+    <t>الرفق</t>
+  </si>
+  <si>
+    <t>Teamwork &amp; Cooperation</t>
+  </si>
+  <si>
+    <t>To help and work well with others for the sake of a greater good</t>
+  </si>
+  <si>
+    <t>التعاون</t>
+  </si>
+  <si>
+    <t>المسؤولية</t>
+  </si>
+  <si>
+    <t>Forbearance &amp; Forgiveness</t>
+  </si>
+  <si>
+    <t>To exercise patience especially when others do wrong or are difficult to deal with</t>
+  </si>
+  <si>
+    <t>الحلم و المغفرة</t>
+  </si>
+  <si>
+    <t>Taqwa</t>
+  </si>
+  <si>
+    <t>To be consious of Allah, and act accordingly</t>
+  </si>
+  <si>
+    <t>التقوة</t>
+  </si>
+  <si>
+    <t>التواضع لله</t>
+  </si>
+  <si>
+    <t>Contentment</t>
+  </si>
+  <si>
+    <t>To be pleased with what you already have and the decree of Allah when it occers (whether good or bad)</t>
+  </si>
+  <si>
+    <t>الرضا</t>
+  </si>
+  <si>
+    <t>Beatuful Perseverance</t>
+  </si>
+  <si>
+    <t>To persevere in challenging situations and turn them into positive experiences</t>
+  </si>
+  <si>
+    <t>صبر جميل</t>
+  </si>
+  <si>
+    <t>Reliance upon Allah</t>
+  </si>
+  <si>
+    <t>To trust Allah and rely upon Him in all matters</t>
+  </si>
+  <si>
+    <t>التوكل على الله</t>
+  </si>
+  <si>
+    <t>Consitency</t>
+  </si>
+  <si>
+    <t>To commit to doing consistent actions and habits – even if they're small</t>
+  </si>
+  <si>
+    <t>المداومة</t>
+  </si>
+  <si>
+    <t>To always work for the eternal afterlife and consider the Akhirah-outcome of actions</t>
+  </si>
+  <si>
+    <t>السعي للاخرة</t>
+  </si>
+  <si>
+    <t>To be mindfully greatful to Allah for the opportunities, and greatful to people around you</t>
+  </si>
+  <si>
+    <t>الشكر</t>
+  </si>
+  <si>
+    <t>Steadfastness upon the truth</t>
+  </si>
+  <si>
+    <t>الثبات على الحق</t>
+  </si>
+  <si>
+    <t>To not fear the truth and its outcomes, to stand firm for the values you believe in</t>
+  </si>
+  <si>
+    <t>Love or the sake of Allah</t>
+  </si>
+  <si>
+    <t>To see the good in people and love them purely for the sake of Allah</t>
+  </si>
+  <si>
+    <t>الحب في الله</t>
+  </si>
+  <si>
+    <t>Purpose- &amp; Impact-driven</t>
+  </si>
+  <si>
+    <t>To be driven by higher purpose and impact, not solely for the short-term results</t>
+  </si>
+  <si>
+    <t>التركيز على الهدف و الاثر</t>
+  </si>
+  <si>
+    <t>Abundance</t>
+  </si>
+  <si>
+    <t>To act recognizing that blessings and bounties are from Allah, and His Kingdom and Blessings are infinite and limitless</t>
+  </si>
+  <si>
+    <t>السعة</t>
+  </si>
+  <si>
+    <t>Introspection &amp; Self-accountability</t>
+  </si>
+  <si>
+    <t>To regularly reflect on your words and actions how they could be better</t>
+  </si>
+  <si>
+    <t>التفكر و المحاسبة</t>
+  </si>
+  <si>
+    <t>Presence</t>
+  </si>
+  <si>
+    <t>To be present mindfully in order to connect deeply with others</t>
+  </si>
+  <si>
+    <t>الحضور</t>
+  </si>
+  <si>
+    <t>Intentionality</t>
+  </si>
+  <si>
+    <t>To remember the intentions behind your actions and renew your intentions often</t>
+  </si>
+  <si>
+    <t>استحضار و تجديد النية</t>
+  </si>
+  <si>
+    <t>Taking initative</t>
+  </si>
+  <si>
+    <t>To take initative in what is beneficial for you in this life and the next, and not hesitate or delay good words or actions</t>
+  </si>
+  <si>
+    <t>الاقدام و السباق في الخير</t>
+  </si>
+  <si>
+    <t>Consult Allah &amp; Others</t>
+  </si>
+  <si>
+    <t>To consult Allah through Istikhara prayer, and seek counsel from relevant people</t>
+  </si>
+  <si>
+    <t>استخارة و استشارة</t>
+  </si>
+  <si>
+    <t>Seek Beneficial Knowledge</t>
+  </si>
+  <si>
+    <t>To commit ro lifelong learning, seeking beneficial knowledge as an act of worship</t>
+  </si>
+  <si>
+    <t>طلب العلم</t>
+  </si>
+  <si>
+    <t>Making Dua</t>
+  </si>
+  <si>
+    <t>دعاء الله</t>
+  </si>
+  <si>
+    <t>Tying ties of kinship</t>
+  </si>
+  <si>
+    <t>To exert sincere effor to remain in touch with your relatives</t>
+  </si>
+  <si>
+    <t>صلة الرحم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eating with people </t>
+  </si>
+  <si>
+    <t>To seek the blessing of eating and sharing your meals with people and never eat alone</t>
+  </si>
+  <si>
+    <t>مشاركة الطعام مع الناس</t>
+  </si>
+  <si>
+    <t>Remembrance of Allah</t>
+  </si>
+  <si>
+    <t>To remember Allah daily and in all prescribed timings/situations</t>
+  </si>
+  <si>
+    <t>ذكر الله</t>
+  </si>
+  <si>
+    <t>To work on making thins things right between people who are in disagreement</t>
+  </si>
+  <si>
+    <t>الاصلاح</t>
+  </si>
+  <si>
+    <t>Tawbah &amp; Constant Returning to Allah</t>
+  </si>
+  <si>
+    <t>التوبة و الانابة</t>
+  </si>
+  <si>
+    <t>Praiseworthy Planning</t>
+  </si>
+  <si>
+    <t>To link good intentions to your plans and have complete trust in Allah in the results</t>
+  </si>
+  <si>
+    <t>التخطيط المحمود</t>
+  </si>
+  <si>
+    <t>Charity</t>
+  </si>
+  <si>
+    <t>To be charitable and give abundantly, generously and consistently without fear of loss</t>
+  </si>
+  <si>
+    <t>الصدقة</t>
+  </si>
+  <si>
+    <t>Salah</t>
+  </si>
+  <si>
+    <t>To prioritize Salah (obligatory/voluntary) with calmness, tranquility, and presence throuout the day</t>
+  </si>
+  <si>
+    <t>الصلاة</t>
+  </si>
+  <si>
+    <t>Quran</t>
+  </si>
+  <si>
+    <t>To spend quality time with the Quran despite a busy schedule and overwhelming responsibilities</t>
+  </si>
+  <si>
+    <t>قراءة القران</t>
+  </si>
+  <si>
+    <t>Waking up Early</t>
+  </si>
+  <si>
+    <t>To seize the barakah in the early hours by starting the day early</t>
+  </si>
+  <si>
+    <t>الاستيقاظ مبكرا</t>
+  </si>
+  <si>
+    <t>Lowering the Gaze</t>
+  </si>
+  <si>
+    <t>To protect your heart by mastering your gaze and not direct your gaze at anything which is unlawful</t>
+  </si>
+  <si>
+    <t>غض البصر</t>
+  </si>
+  <si>
+    <t>Controlling the tounge</t>
+  </si>
+  <si>
+    <t>To think before speaking and speak only when speech is better than silence</t>
+  </si>
+  <si>
+    <t>امساك اللسان</t>
+  </si>
+  <si>
+    <t>Helping people</t>
+  </si>
+  <si>
+    <t>To be consious of people's needs and hsten to lend the helping hand before you are asked</t>
+  </si>
+  <si>
+    <t>مساعدة الناس</t>
+  </si>
+  <si>
+    <t>Sending salawat upon the Prophet</t>
+  </si>
+  <si>
+    <t>To send abundant salawat upon the Prophet (PBUH) daily</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الصلاة على النبي </t>
   </si>
 </sst>
 </file>
@@ -484,42 +871,199 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{203D4031-030A-8E41-8624-2D4A4A440568}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" customWidth="1"/>
+    <col min="3" max="3" width="60.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -529,42 +1073,199 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9481DD4B-4E3C-A342-BACB-60CFCC22DA47}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="66.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>61</v>
+      </c>
+      <c r="B2" t="s">
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>65</v>
+      </c>
+      <c r="B4" t="s">
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C12" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" t="s">
+        <v>92</v>
+      </c>
+      <c r="C13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>93</v>
+      </c>
+      <c r="B14" t="s">
+        <v>95</v>
+      </c>
+      <c r="C14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>96</v>
+      </c>
+      <c r="B15" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B16" t="s">
+        <v>101</v>
+      </c>
+      <c r="C16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -574,42 +1275,199 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B53CC270-253C-2240-9850-D5FA3E7DF669}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="31.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="81.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>16</v>
+        <v>105</v>
       </c>
       <c r="B1" t="s">
-        <v>17</v>
+        <v>107</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>108</v>
+      </c>
+      <c r="B2" t="s">
+        <v>110</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>111</v>
+      </c>
+      <c r="B3" t="s">
+        <v>112</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>113</v>
+      </c>
+      <c r="B4" t="s">
+        <v>115</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C9" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C10" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>132</v>
+      </c>
+      <c r="B11" t="s">
+        <v>134</v>
+      </c>
+      <c r="C11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>135</v>
+      </c>
+      <c r="B12" t="s">
+        <v>137</v>
+      </c>
+      <c r="C12" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B13" t="s">
+        <v>140</v>
+      </c>
+      <c r="C13" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>141</v>
+      </c>
+      <c r="B14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C14" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>144</v>
+      </c>
+      <c r="B15" t="s">
+        <v>146</v>
+      </c>
+      <c r="C15" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>147</v>
+      </c>
+      <c r="B16" t="s">
+        <v>149</v>
+      </c>
+      <c r="C16" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>150</v>
+      </c>
+      <c r="B17" t="s">
+        <v>152</v>
+      </c>
+      <c r="C17" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
